--- a/docs/MVB/铁八（HXD1）/DK2(HXD1)/乌鲁木齐-KD2(HXD1C).xlsx
+++ b/docs/MVB/铁八（HXD1）/DK2(HXD1)/乌鲁木齐-KD2(HXD1C).xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$1</definedName>
     <definedName name="OLE_LINK4" localSheetId="0">Sheet1!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="202">
   <si>
     <t>信号名称</t>
   </si>
@@ -470,19 +470,192 @@
   <si>
     <t>0x706</t>
   </si>
+  <si>
+    <t>BCU生命信号</t>
+  </si>
+  <si>
+    <t>0x137</t>
+  </si>
+  <si>
+    <t>本机</t>
+  </si>
+  <si>
+    <t>制动阀切除</t>
+  </si>
+  <si>
+    <t>惩罚制动</t>
+  </si>
+  <si>
+    <t>紧急制动</t>
+  </si>
+  <si>
+    <t>制动机类型bit0</t>
+  </si>
+  <si>
+    <t>制动机类型bit1</t>
+  </si>
+  <si>
+    <t>制动机类型bit2</t>
+  </si>
+  <si>
+    <t>大闸运转</t>
+  </si>
+  <si>
+    <t>大闸最小制动</t>
+  </si>
+  <si>
+    <t>大闸常用制动</t>
+  </si>
+  <si>
+    <t>大闸全制动</t>
+  </si>
+  <si>
+    <t>大闸抑制</t>
+  </si>
+  <si>
+    <t>大闸重联</t>
+  </si>
+  <si>
+    <t>大闸紧急</t>
+  </si>
+  <si>
+    <t>小闸运转</t>
+  </si>
+  <si>
+    <t>小闸制动区</t>
+  </si>
+  <si>
+    <t>小闸全制动</t>
+  </si>
+  <si>
+    <t>小闸单缓激活</t>
+  </si>
+  <si>
+    <t>均衡缸压力</t>
+  </si>
+  <si>
+    <t>大闸目标值</t>
+  </si>
+  <si>
+    <t>进入DP模式</t>
+  </si>
+  <si>
+    <t>漏泄测试中</t>
+  </si>
+  <si>
+    <t>BCU自身惩罚制动请求bit0</t>
+  </si>
+  <si>
+    <t>BCU自身惩罚制动请求bit1</t>
+  </si>
+  <si>
+    <t>列车管压力有效</t>
+  </si>
+  <si>
+    <t>总风压力有效</t>
+  </si>
+  <si>
+    <t>均衡压力有效</t>
+  </si>
+  <si>
+    <t>流量有效</t>
+  </si>
+  <si>
+    <t>大闸目标值有效</t>
+  </si>
+  <si>
+    <t>小闸目标值有效</t>
+  </si>
+  <si>
+    <t>小闸目标值</t>
+  </si>
+  <si>
+    <t>BCU软件版本</t>
+  </si>
+  <si>
+    <t>A08 总分低于500kPa故障</t>
+  </si>
+  <si>
+    <t>A09大闸制动，制动缸压力失效故障</t>
+  </si>
+  <si>
+    <t>A10小闸制动，制动缸压力失效故障</t>
+  </si>
+  <si>
+    <t>A11 均衡无法减压故障</t>
+  </si>
+  <si>
+    <t>A13 大小闸失效故障</t>
+  </si>
+  <si>
+    <t>RDP生命信号</t>
+  </si>
+  <si>
+    <t>0x421</t>
+  </si>
+  <si>
+    <t>惩罚制动请求</t>
+  </si>
+  <si>
+    <t>紧急制动请求</t>
+  </si>
+  <si>
+    <t>单缓请求</t>
+  </si>
+  <si>
+    <t>泄漏测试请求</t>
+  </si>
+  <si>
+    <t>制动阀切除 0-投入，1-切除</t>
+  </si>
+  <si>
+    <t>从控车BCU惩罚制动标记</t>
+  </si>
+  <si>
+    <t>初制动</t>
+  </si>
+  <si>
+    <t>漏泄状态1</t>
+  </si>
+  <si>
+    <t>漏泄状态2</t>
+  </si>
+  <si>
+    <t>RDP类型bit0</t>
+  </si>
+  <si>
+    <t>RDP类型bit1</t>
+  </si>
+  <si>
+    <t>惩罚制动请求1-惩罚80</t>
+  </si>
+  <si>
+    <t>惩罚制动请求2-惩罚到0</t>
+  </si>
+  <si>
+    <t>机车模式-从控</t>
+  </si>
+  <si>
+    <t>机车模式-主控</t>
+  </si>
+  <si>
+    <t>DP模式有效位</t>
+  </si>
+  <si>
+    <t>零速</t>
+  </si>
+  <si>
+    <t>0x021</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0000_);[Red]\(0.0000\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0.0000_);[Red]\(0.0000\)"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -526,151 +699,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -683,194 +718,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -908,253 +757,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1195,14 +802,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1219,58 +826,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1561,14 +1124,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:N251"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N392"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="33.625" style="2" customWidth="1"/>
     <col min="2" max="2" width="11.125" style="3" customWidth="1"/>
@@ -1586,7 +1149,7 @@
     <col min="14" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="56.25" customHeight="1" spans="1:13">
+    <row r="1" spans="1:13" ht="56.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1627,7 +1190,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2" s="15" t="s">
         <v>13</v>
       </c>
@@ -1666,7 +1229,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3" s="15" t="s">
         <v>18</v>
       </c>
@@ -1702,7 +1265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4" s="15" t="s">
         <v>21</v>
       </c>
@@ -1741,7 +1304,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5" s="15" t="s">
         <v>24</v>
       </c>
@@ -1780,7 +1343,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6" s="15" t="s">
         <v>26</v>
       </c>
@@ -1819,7 +1382,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7" s="15" t="s">
         <v>27</v>
       </c>
@@ -1858,7 +1421,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A8" s="15" t="s">
         <v>29</v>
       </c>
@@ -1897,7 +1460,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9" s="15" t="s">
         <v>31</v>
       </c>
@@ -1936,7 +1499,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A10" s="15" t="s">
         <v>33</v>
       </c>
@@ -1975,7 +1538,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A11" s="15" t="s">
         <v>35</v>
       </c>
@@ -2014,7 +1577,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A12" s="15" t="s">
         <v>37</v>
       </c>
@@ -2053,7 +1616,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A13" s="15" t="s">
         <v>37</v>
       </c>
@@ -2089,7 +1652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A14" s="15" t="s">
         <v>38</v>
       </c>
@@ -2128,7 +1691,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A15" s="15" t="s">
         <v>40</v>
       </c>
@@ -2167,7 +1730,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16" s="15" t="s">
         <v>37</v>
       </c>
@@ -2204,7 +1767,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A17" s="15" t="s">
         <v>42</v>
       </c>
@@ -2241,7 +1804,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A18" s="15" t="s">
         <v>44</v>
       </c>
@@ -2280,7 +1843,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A19" s="15" t="s">
         <v>46</v>
       </c>
@@ -2319,7 +1882,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A20" s="15" t="s">
         <v>37</v>
       </c>
@@ -2353,7 +1916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A21" s="15" t="s">
         <v>48</v>
       </c>
@@ -2390,7 +1953,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A22" s="15" t="s">
         <v>50</v>
       </c>
@@ -2427,7 +1990,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A23" s="15" t="s">
         <v>52</v>
       </c>
@@ -2464,7 +2027,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A24" s="15" t="s">
         <v>54</v>
       </c>
@@ -2501,7 +2064,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A25" s="15" t="s">
         <v>55</v>
       </c>
@@ -2538,7 +2101,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A26" s="15" t="s">
         <v>56</v>
       </c>
@@ -2575,7 +2138,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A27" s="15" t="s">
         <v>37</v>
       </c>
@@ -2609,7 +2172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="1:14">
+    <row r="28" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A28" s="15" t="s">
         <v>57</v>
       </c>
@@ -2630,7 +2193,7 @@
       </c>
       <c r="G28" s="21"/>
       <c r="H28" s="19">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="I28" s="4" t="b">
         <v>0</v>
@@ -2649,7 +2212,7 @@
       </c>
       <c r="N28" s="23"/>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A29" s="15" t="s">
         <v>61</v>
       </c>
@@ -2670,7 +2233,7 @@
       </c>
       <c r="G29" s="18"/>
       <c r="H29" s="19">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="I29" s="4" t="b">
         <v>0</v>
@@ -2688,7 +2251,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A30" s="15" t="s">
         <v>62</v>
       </c>
@@ -2709,7 +2272,7 @@
       </c>
       <c r="G30" s="18"/>
       <c r="H30" s="19">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="I30" s="4" t="b">
         <v>0</v>
@@ -2727,7 +2290,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A31" s="15" t="s">
         <v>63</v>
       </c>
@@ -2748,7 +2311,7 @@
       </c>
       <c r="G31" s="18"/>
       <c r="H31" s="19">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="I31" s="4" t="b">
         <v>0</v>
@@ -2766,7 +2329,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A32" s="15" t="s">
         <v>64</v>
       </c>
@@ -2787,7 +2350,7 @@
       </c>
       <c r="G32" s="18"/>
       <c r="H32" s="19">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="I32" s="4" t="b">
         <v>0</v>
@@ -2805,7 +2368,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" ht="16.5" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A33" s="15" t="s">
         <v>65</v>
       </c>
@@ -2826,7 +2389,7 @@
       </c>
       <c r="G33" s="18"/>
       <c r="H33" s="19">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="I33" s="20" t="b">
         <v>0</v>
@@ -2844,7 +2407,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A34" s="15" t="s">
         <v>67</v>
       </c>
@@ -2883,7 +2446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A35" s="15" t="s">
         <v>68</v>
       </c>
@@ -2922,7 +2485,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A36" s="15" t="s">
         <v>70</v>
       </c>
@@ -2961,7 +2524,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A37" s="15" t="s">
         <v>71</v>
       </c>
@@ -3000,7 +2563,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A38" s="15" t="s">
         <v>72</v>
       </c>
@@ -3039,7 +2602,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A39" s="15" t="s">
         <v>73</v>
       </c>
@@ -3078,7 +2641,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A40" s="15" t="s">
         <v>37</v>
       </c>
@@ -3117,7 +2680,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A41" s="15" t="s">
         <v>37</v>
       </c>
@@ -3156,7 +2719,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A42" s="15" t="s">
         <v>37</v>
       </c>
@@ -3195,7 +2758,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A43" s="15" t="s">
         <v>74</v>
       </c>
@@ -3234,7 +2797,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A44" s="15" t="s">
         <v>75</v>
       </c>
@@ -3273,7 +2836,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A45" s="15" t="s">
         <v>76</v>
       </c>
@@ -3312,7 +2875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A46" s="15" t="s">
         <v>77</v>
       </c>
@@ -3351,7 +2914,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A47" s="15" t="s">
         <v>78</v>
       </c>
@@ -3390,7 +2953,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A48" s="15" t="s">
         <v>79</v>
       </c>
@@ -3429,7 +2992,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A49" s="15" t="s">
         <v>80</v>
       </c>
@@ -3468,7 +3031,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A50" s="15" t="s">
         <v>38</v>
       </c>
@@ -3507,7 +3070,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A51" s="15" t="s">
         <v>40</v>
       </c>
@@ -3546,7 +3109,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" ht="54" spans="1:13">
+    <row r="52" spans="1:13" ht="54" x14ac:dyDescent="0.15">
       <c r="A52" s="15" t="s">
         <v>83</v>
       </c>
@@ -3585,7 +3148,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" ht="27" spans="1:13">
+    <row r="53" spans="1:13" ht="27" x14ac:dyDescent="0.15">
       <c r="A53" s="15" t="s">
         <v>85</v>
       </c>
@@ -3624,7 +3187,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="54" ht="27" spans="1:13">
+    <row r="54" spans="1:13" ht="27" x14ac:dyDescent="0.15">
       <c r="A54" s="15" t="s">
         <v>87</v>
       </c>
@@ -3663,7 +3226,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A55" s="15" t="s">
         <v>89</v>
       </c>
@@ -3702,7 +3265,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A56" s="15" t="s">
         <v>90</v>
       </c>
@@ -3741,7 +3304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A57" s="15" t="s">
         <v>91</v>
       </c>
@@ -3780,7 +3343,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A58" s="15" t="s">
         <v>92</v>
       </c>
@@ -3819,7 +3382,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A59" s="15" t="s">
         <v>94</v>
       </c>
@@ -3858,7 +3421,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A60" s="15" t="s">
         <v>96</v>
       </c>
@@ -3897,7 +3460,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A61" s="15" t="s">
         <v>98</v>
       </c>
@@ -3936,7 +3499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A62" s="15" t="s">
         <v>99</v>
       </c>
@@ -3975,7 +3538,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A63" s="15" t="s">
         <v>100</v>
       </c>
@@ -4014,7 +3577,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A64" s="15" t="s">
         <v>101</v>
       </c>
@@ -4053,7 +3616,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A65" s="15" t="s">
         <v>102</v>
       </c>
@@ -4092,7 +3655,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A66" s="15" t="s">
         <v>103</v>
       </c>
@@ -4131,7 +3694,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A67" s="15" t="s">
         <v>37</v>
       </c>
@@ -4170,7 +3733,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A68" s="15" t="s">
         <v>96</v>
       </c>
@@ -4209,7 +3772,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A69" s="15" t="s">
         <v>99</v>
       </c>
@@ -4248,7 +3811,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A70" s="15" t="s">
         <v>100</v>
       </c>
@@ -4287,7 +3850,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A71" s="15" t="s">
         <v>37</v>
       </c>
@@ -4326,7 +3889,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A72" s="15" t="s">
         <v>37</v>
       </c>
@@ -4365,7 +3928,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A73" s="15" t="s">
         <v>37</v>
       </c>
@@ -4404,7 +3967,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A74" s="15" t="s">
         <v>37</v>
       </c>
@@ -4443,7 +4006,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A75" s="15" t="s">
         <v>37</v>
       </c>
@@ -4482,7 +4045,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A76" s="15" t="s">
         <v>104</v>
       </c>
@@ -4521,7 +4084,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A77" s="15" t="s">
         <v>37</v>
       </c>
@@ -4560,7 +4123,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A78" s="15" t="s">
         <v>37</v>
       </c>
@@ -4599,7 +4162,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A79" s="15" t="s">
         <v>37</v>
       </c>
@@ -4638,7 +4201,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A80" s="15" t="s">
         <v>37</v>
       </c>
@@ -4677,7 +4240,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A81" s="15" t="s">
         <v>37</v>
       </c>
@@ -4716,7 +4279,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A82" s="15" t="s">
         <v>37</v>
       </c>
@@ -4755,7 +4318,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A83" s="15" t="s">
         <v>37</v>
       </c>
@@ -4794,7 +4357,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A84" s="15" t="s">
         <v>37</v>
       </c>
@@ -4833,7 +4396,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A85" s="15" t="s">
         <v>105</v>
       </c>
@@ -4872,7 +4435,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A86" s="15" t="s">
         <v>106</v>
       </c>
@@ -4911,7 +4474,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A87" s="15" t="s">
         <v>46</v>
       </c>
@@ -4948,7 +4511,7 @@
       </c>
       <c r="M87" s="15"/>
     </row>
-    <row r="88" ht="15" spans="1:13">
+    <row r="88" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A88" s="15" t="s">
         <v>107</v>
       </c>
@@ -4984,7 +4547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" ht="15" spans="1:13">
+    <row r="89" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A89" s="15" t="s">
         <v>107</v>
       </c>
@@ -5020,7 +4583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" ht="15" spans="1:13">
+    <row r="90" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A90" s="15" t="s">
         <v>109</v>
       </c>
@@ -5056,7 +4619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" ht="15" spans="1:13">
+    <row r="91" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A91" s="15" t="s">
         <v>44</v>
       </c>
@@ -5092,7 +4655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" ht="15" spans="1:13">
+    <row r="92" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A92" s="15" t="s">
         <v>37</v>
       </c>
@@ -5128,7 +4691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" ht="15" spans="1:13">
+    <row r="93" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A93" s="15" t="s">
         <v>110</v>
       </c>
@@ -5164,7 +4727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" ht="15" spans="1:13">
+    <row r="94" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A94" s="16" t="s">
         <v>111</v>
       </c>
@@ -5200,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" ht="15" spans="1:13">
+    <row r="95" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A95" s="16" t="s">
         <v>112</v>
       </c>
@@ -5236,7 +4799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" ht="15" spans="1:13">
+    <row r="96" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A96" s="16" t="s">
         <v>113</v>
       </c>
@@ -5272,7 +4835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" ht="15" spans="1:12">
+    <row r="97" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A97" s="16" t="s">
         <v>114</v>
       </c>
@@ -5308,7 +4871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" ht="15" spans="1:12">
+    <row r="98" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A98" s="16" t="s">
         <v>27</v>
       </c>
@@ -5344,7 +4907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" ht="15" spans="1:12">
+    <row r="99" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A99" s="16" t="s">
         <v>29</v>
       </c>
@@ -5380,7 +4943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" ht="15" spans="1:12">
+    <row r="100" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A100" s="16" t="s">
         <v>37</v>
       </c>
@@ -5416,7 +4979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" ht="15" spans="1:12">
+    <row r="101" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A101" s="16" t="s">
         <v>37</v>
       </c>
@@ -5452,7 +5015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" ht="15" spans="1:12">
+    <row r="102" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A102" s="16" t="s">
         <v>37</v>
       </c>
@@ -5488,7 +5051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" ht="15" spans="1:12">
+    <row r="103" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A103" s="16" t="s">
         <v>115</v>
       </c>
@@ -5524,7 +5087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" ht="15" spans="1:12">
+    <row r="104" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A104" s="16" t="s">
         <v>37</v>
       </c>
@@ -5560,7 +5123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" ht="15" spans="1:12">
+    <row r="105" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A105" s="16" t="s">
         <v>37</v>
       </c>
@@ -5596,7 +5159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" ht="15" spans="1:12">
+    <row r="106" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A106" s="16" t="s">
         <v>37</v>
       </c>
@@ -5632,7 +5195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" ht="15" spans="1:12">
+    <row r="107" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A107" s="16" t="s">
         <v>37</v>
       </c>
@@ -5668,7 +5231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" ht="15" spans="1:12">
+    <row r="108" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A108" s="16" t="s">
         <v>37</v>
       </c>
@@ -5704,7 +5267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" ht="15" spans="1:12">
+    <row r="109" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A109" s="16" t="s">
         <v>37</v>
       </c>
@@ -5740,7 +5303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" ht="15" spans="1:12">
+    <row r="110" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A110" s="16" t="s">
         <v>37</v>
       </c>
@@ -5776,7 +5339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" ht="15" spans="1:12">
+    <row r="111" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A111" s="16" t="s">
         <v>37</v>
       </c>
@@ -5812,7 +5375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" ht="15" spans="1:12">
+    <row r="112" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A112" s="16" t="s">
         <v>37</v>
       </c>
@@ -5848,7 +5411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" ht="15" spans="1:12">
+    <row r="113" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A113" s="16" t="s">
         <v>37</v>
       </c>
@@ -5884,7 +5447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" ht="15" spans="1:12">
+    <row r="114" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A114" s="16" t="s">
         <v>37</v>
       </c>
@@ -5920,7 +5483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" ht="15" spans="1:12">
+    <row r="115" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A115" s="16" t="s">
         <v>37</v>
       </c>
@@ -5956,7 +5519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" ht="15" spans="1:12">
+    <row r="116" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A116" s="16" t="s">
         <v>37</v>
       </c>
@@ -5992,7 +5555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" ht="15" spans="1:12">
+    <row r="117" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A117" s="16" t="s">
         <v>37</v>
       </c>
@@ -6028,7 +5591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" ht="15" spans="1:12">
+    <row r="118" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A118" s="16" t="s">
         <v>37</v>
       </c>
@@ -6064,7 +5627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" ht="15" spans="1:12">
+    <row r="119" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A119" s="16" t="s">
         <v>46</v>
       </c>
@@ -6100,7 +5663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" ht="15" spans="1:12">
+    <row r="120" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A120" s="16" t="s">
         <v>107</v>
       </c>
@@ -6136,7 +5699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" ht="15" spans="1:12">
+    <row r="121" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A121" s="16" t="s">
         <v>107</v>
       </c>
@@ -6172,7 +5735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" ht="15" spans="1:12">
+    <row r="122" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A122" s="16" t="s">
         <v>109</v>
       </c>
@@ -6208,7 +5771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" ht="15" spans="1:12">
+    <row r="123" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A123" s="16" t="s">
         <v>44</v>
       </c>
@@ -6244,7 +5807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" ht="15" spans="1:12">
+    <row r="124" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A124" s="16" t="s">
         <v>37</v>
       </c>
@@ -6280,7 +5843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" ht="15" spans="1:12">
+    <row r="125" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A125" s="16" t="s">
         <v>110</v>
       </c>
@@ -6316,7 +5879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" ht="15" spans="1:12">
+    <row r="126" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A126" s="16" t="s">
         <v>111</v>
       </c>
@@ -6352,7 +5915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" ht="15" spans="1:12">
+    <row r="127" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A127" s="16" t="s">
         <v>112</v>
       </c>
@@ -6388,7 +5951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" ht="15" spans="1:12">
+    <row r="128" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A128" s="16" t="s">
         <v>113</v>
       </c>
@@ -6424,7 +5987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" ht="15" spans="1:12">
+    <row r="129" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A129" s="16" t="s">
         <v>114</v>
       </c>
@@ -6460,7 +6023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" ht="15" spans="1:12">
+    <row r="130" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A130" s="16" t="s">
         <v>27</v>
       </c>
@@ -6496,7 +6059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" ht="15" spans="1:12">
+    <row r="131" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A131" s="16" t="s">
         <v>29</v>
       </c>
@@ -6532,7 +6095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" ht="15" spans="1:12">
+    <row r="132" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A132" s="16" t="s">
         <v>37</v>
       </c>
@@ -6568,7 +6131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" ht="15" spans="1:12">
+    <row r="133" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A133" s="16" t="s">
         <v>37</v>
       </c>
@@ -6604,7 +6167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" ht="15" spans="1:12">
+    <row r="134" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A134" s="16" t="s">
         <v>37</v>
       </c>
@@ -6640,7 +6203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" ht="15" spans="1:12">
+    <row r="135" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A135" s="16" t="s">
         <v>115</v>
       </c>
@@ -6676,7 +6239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" ht="15" spans="1:12">
+    <row r="136" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A136" s="16" t="s">
         <v>37</v>
       </c>
@@ -6712,7 +6275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" ht="15" spans="1:12">
+    <row r="137" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A137" s="16" t="s">
         <v>37</v>
       </c>
@@ -6748,7 +6311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" ht="15" spans="1:12">
+    <row r="138" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A138" s="16" t="s">
         <v>37</v>
       </c>
@@ -6784,7 +6347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" ht="15" spans="1:12">
+    <row r="139" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A139" s="16" t="s">
         <v>37</v>
       </c>
@@ -6820,7 +6383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" ht="15" spans="1:12">
+    <row r="140" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A140" s="16" t="s">
         <v>37</v>
       </c>
@@ -6856,7 +6419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" ht="15" spans="1:12">
+    <row r="141" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A141" s="16" t="s">
         <v>37</v>
       </c>
@@ -6892,7 +6455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" ht="15" spans="1:12">
+    <row r="142" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A142" s="16" t="s">
         <v>37</v>
       </c>
@@ -6928,7 +6491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" ht="15" spans="1:12">
+    <row r="143" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A143" s="16" t="s">
         <v>37</v>
       </c>
@@ -6964,7 +6527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" ht="15" spans="1:12">
+    <row r="144" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A144" s="16" t="s">
         <v>37</v>
       </c>
@@ -7000,7 +6563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" ht="15" spans="1:12">
+    <row r="145" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A145" s="16" t="s">
         <v>37</v>
       </c>
@@ -7036,7 +6599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" ht="15" spans="1:12">
+    <row r="146" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A146" s="16" t="s">
         <v>37</v>
       </c>
@@ -7072,7 +6635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" ht="15" spans="1:12">
+    <row r="147" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A147" s="16" t="s">
         <v>37</v>
       </c>
@@ -7108,7 +6671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" ht="15" spans="1:12">
+    <row r="148" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A148" s="16" t="s">
         <v>37</v>
       </c>
@@ -7144,7 +6707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" ht="15" spans="1:12">
+    <row r="149" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A149" s="16" t="s">
         <v>37</v>
       </c>
@@ -7180,7 +6743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" ht="15" spans="1:12">
+    <row r="150" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A150" s="16" t="s">
         <v>37</v>
       </c>
@@ -7216,7 +6779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" ht="15" spans="1:12">
+    <row r="151" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A151" s="16" t="s">
         <v>46</v>
       </c>
@@ -7252,7 +6815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" ht="15" spans="1:12">
+    <row r="152" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A152" s="16" t="s">
         <v>107</v>
       </c>
@@ -7288,7 +6851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" ht="15" spans="1:12">
+    <row r="153" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A153" s="16" t="s">
         <v>109</v>
       </c>
@@ -7324,7 +6887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" ht="15" spans="1:12">
+    <row r="154" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A154" s="16" t="s">
         <v>44</v>
       </c>
@@ -7360,7 +6923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" ht="15" spans="1:12">
+    <row r="155" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A155" s="16" t="s">
         <v>118</v>
       </c>
@@ -7396,7 +6959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" ht="15" spans="1:12">
+    <row r="156" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A156" s="16" t="s">
         <v>118</v>
       </c>
@@ -7432,7 +6995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" ht="15" spans="1:12">
+    <row r="157" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A157" s="16" t="s">
         <v>37</v>
       </c>
@@ -7468,7 +7031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" ht="15" spans="1:12">
+    <row r="158" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A158" s="16" t="s">
         <v>119</v>
       </c>
@@ -7504,7 +7067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" ht="15" spans="1:12">
+    <row r="159" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A159" s="16" t="s">
         <v>120</v>
       </c>
@@ -7540,7 +7103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" ht="15" spans="1:12">
+    <row r="160" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A160" s="16" t="s">
         <v>121</v>
       </c>
@@ -7576,7 +7139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" ht="15" spans="1:12">
+    <row r="161" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A161" s="16" t="s">
         <v>122</v>
       </c>
@@ -7612,7 +7175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" ht="15" spans="1:12">
+    <row r="162" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A162" s="16" t="s">
         <v>123</v>
       </c>
@@ -7648,7 +7211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" ht="15" spans="1:12">
+    <row r="163" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A163" s="16" t="s">
         <v>124</v>
       </c>
@@ -7684,7 +7247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" ht="15" spans="1:12">
+    <row r="164" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A164" s="16" t="s">
         <v>37</v>
       </c>
@@ -7720,7 +7283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" ht="15" spans="1:12">
+    <row r="165" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A165" s="16" t="s">
         <v>37</v>
       </c>
@@ -7756,7 +7319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" ht="15" spans="1:12">
+    <row r="166" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A166" s="16" t="s">
         <v>125</v>
       </c>
@@ -7792,7 +7355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" ht="15" spans="1:12">
+    <row r="167" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A167" s="16" t="s">
         <v>126</v>
       </c>
@@ -7828,7 +7391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" ht="15" spans="1:12">
+    <row r="168" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A168" s="16" t="s">
         <v>127</v>
       </c>
@@ -7864,7 +7427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" ht="15" spans="1:12">
+    <row r="169" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A169" s="16" t="s">
         <v>128</v>
       </c>
@@ -7900,7 +7463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" ht="15" spans="1:12">
+    <row r="170" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A170" s="16" t="s">
         <v>129</v>
       </c>
@@ -7936,7 +7499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" ht="15" spans="1:12">
+    <row r="171" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A171" s="16" t="s">
         <v>37</v>
       </c>
@@ -7972,7 +7535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" ht="15" spans="1:12">
+    <row r="172" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A172" s="16" t="s">
         <v>37</v>
       </c>
@@ -8008,7 +7571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" ht="15" spans="1:12">
+    <row r="173" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A173" s="16" t="s">
         <v>37</v>
       </c>
@@ -8044,7 +7607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" ht="15" spans="1:12">
+    <row r="174" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A174" s="16" t="s">
         <v>37</v>
       </c>
@@ -8080,7 +7643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" ht="15" spans="1:12">
+    <row r="175" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A175" s="16" t="s">
         <v>130</v>
       </c>
@@ -8116,7 +7679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" ht="15" spans="1:12">
+    <row r="176" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A176" s="16" t="s">
         <v>37</v>
       </c>
@@ -8152,7 +7715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" ht="15" spans="1:12">
+    <row r="177" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A177" s="16" t="s">
         <v>37</v>
       </c>
@@ -8188,7 +7751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" ht="15" spans="1:12">
+    <row r="178" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A178" s="16" t="s">
         <v>37</v>
       </c>
@@ -8224,7 +7787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" ht="15" spans="1:12">
+    <row r="179" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A179" s="16" t="s">
         <v>37</v>
       </c>
@@ -8260,7 +7823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" ht="15" spans="1:12">
+    <row r="180" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A180" s="16" t="s">
         <v>37</v>
       </c>
@@ -8296,7 +7859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" ht="15" spans="1:12">
+    <row r="181" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A181" s="16" t="s">
         <v>37</v>
       </c>
@@ -8332,7 +7895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" ht="15" spans="1:12">
+    <row r="182" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A182" s="16" t="s">
         <v>131</v>
       </c>
@@ -8368,7 +7931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" ht="15" spans="1:12">
+    <row r="183" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A183" s="16" t="s">
         <v>132</v>
       </c>
@@ -8404,7 +7967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" ht="15" spans="1:12">
+    <row r="184" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A184" s="16" t="s">
         <v>133</v>
       </c>
@@ -8440,7 +8003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" ht="15" spans="1:12">
+    <row r="185" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A185" s="16" t="s">
         <v>134</v>
       </c>
@@ -8476,7 +8039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" ht="15" spans="1:12">
+    <row r="186" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A186" s="16" t="s">
         <v>135</v>
       </c>
@@ -8512,7 +8075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" ht="15" spans="1:12">
+    <row r="187" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A187" s="16" t="s">
         <v>136</v>
       </c>
@@ -8548,7 +8111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" ht="15" spans="1:12">
+    <row r="188" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A188" s="16" t="s">
         <v>137</v>
       </c>
@@ -8584,7 +8147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" ht="15" spans="1:12">
+    <row r="189" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A189" s="16" t="s">
         <v>37</v>
       </c>
@@ -8620,7 +8183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" ht="15" spans="1:12">
+    <row r="190" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A190" s="16" t="s">
         <v>138</v>
       </c>
@@ -8656,7 +8219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" ht="15" spans="1:12">
+    <row r="191" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A191" s="16" t="s">
         <v>139</v>
       </c>
@@ -8692,7 +8255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" ht="15" spans="1:12">
+    <row r="192" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A192" s="16" t="s">
         <v>140</v>
       </c>
@@ -8728,7 +8291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" ht="15" spans="1:12">
+    <row r="193" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A193" s="16" t="s">
         <v>141</v>
       </c>
@@ -8764,7 +8327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" ht="15" spans="1:12">
+    <row r="194" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A194" s="16" t="s">
         <v>37</v>
       </c>
@@ -8800,7 +8363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" ht="15" spans="1:12">
+    <row r="195" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A195" s="16" t="s">
         <v>37</v>
       </c>
@@ -8836,7 +8399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" ht="15" spans="1:12">
+    <row r="196" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A196" s="16" t="s">
         <v>37</v>
       </c>
@@ -8872,7 +8435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" ht="15" spans="1:12">
+    <row r="197" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A197" s="16" t="s">
         <v>37</v>
       </c>
@@ -8908,7 +8471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" ht="15" spans="1:12">
+    <row r="198" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A198" s="16" t="s">
         <v>46</v>
       </c>
@@ -8944,7 +8507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" ht="15" spans="1:12">
+    <row r="199" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A199" s="16" t="s">
         <v>107</v>
       </c>
@@ -8980,7 +8543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" ht="15" spans="1:12">
+    <row r="200" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A200" s="16" t="s">
         <v>109</v>
       </c>
@@ -9016,7 +8579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" ht="15" spans="1:12">
+    <row r="201" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A201" s="16" t="s">
         <v>44</v>
       </c>
@@ -9052,7 +8615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" ht="15" spans="1:12">
+    <row r="202" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A202" s="16" t="s">
         <v>118</v>
       </c>
@@ -9088,7 +8651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" ht="15" spans="1:12">
+    <row r="203" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A203" s="16" t="s">
         <v>118</v>
       </c>
@@ -9124,7 +8687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" ht="15" spans="1:12">
+    <row r="204" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A204" s="16" t="s">
         <v>37</v>
       </c>
@@ -9160,7 +8723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" ht="15" spans="1:12">
+    <row r="205" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A205" s="16" t="s">
         <v>119</v>
       </c>
@@ -9196,7 +8759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" ht="15" spans="1:12">
+    <row r="206" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A206" s="16" t="s">
         <v>120</v>
       </c>
@@ -9232,7 +8795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" ht="15" spans="1:12">
+    <row r="207" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A207" s="16" t="s">
         <v>121</v>
       </c>
@@ -9268,7 +8831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" ht="15" spans="1:12">
+    <row r="208" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A208" s="16" t="s">
         <v>122</v>
       </c>
@@ -9304,7 +8867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" ht="15" spans="1:12">
+    <row r="209" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A209" s="16" t="s">
         <v>123</v>
       </c>
@@ -9340,7 +8903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" ht="15" spans="1:12">
+    <row r="210" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A210" s="16" t="s">
         <v>124</v>
       </c>
@@ -9376,7 +8939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" ht="15" spans="1:12">
+    <row r="211" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A211" s="16" t="s">
         <v>37</v>
       </c>
@@ -9412,7 +8975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" ht="15" spans="1:12">
+    <row r="212" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A212" s="16" t="s">
         <v>37</v>
       </c>
@@ -9448,7 +9011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" ht="15" spans="1:12">
+    <row r="213" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A213" s="16" t="s">
         <v>125</v>
       </c>
@@ -9484,7 +9047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" ht="15" spans="1:12">
+    <row r="214" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A214" s="16" t="s">
         <v>126</v>
       </c>
@@ -9520,7 +9083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" ht="15" spans="1:12">
+    <row r="215" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A215" s="16" t="s">
         <v>127</v>
       </c>
@@ -9556,7 +9119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" ht="15" spans="1:12">
+    <row r="216" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A216" s="16" t="s">
         <v>128</v>
       </c>
@@ -9592,7 +9155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" ht="15" spans="1:12">
+    <row r="217" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A217" s="16" t="s">
         <v>129</v>
       </c>
@@ -9628,7 +9191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" ht="15" spans="1:12">
+    <row r="218" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A218" s="16" t="s">
         <v>37</v>
       </c>
@@ -9664,7 +9227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" ht="15" spans="1:12">
+    <row r="219" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A219" s="16" t="s">
         <v>37</v>
       </c>
@@ -9700,7 +9263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" ht="15" spans="1:12">
+    <row r="220" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A220" s="16" t="s">
         <v>37</v>
       </c>
@@ -9736,7 +9299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" ht="15" spans="1:12">
+    <row r="221" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A221" s="16" t="s">
         <v>37</v>
       </c>
@@ -9772,7 +9335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" ht="15" spans="1:12">
+    <row r="222" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A222" s="16" t="s">
         <v>130</v>
       </c>
@@ -9808,7 +9371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" ht="15" spans="1:12">
+    <row r="223" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A223" s="16" t="s">
         <v>37</v>
       </c>
@@ -9844,7 +9407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" ht="15" spans="1:12">
+    <row r="224" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A224" s="16" t="s">
         <v>37</v>
       </c>
@@ -9880,7 +9443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" ht="15" spans="1:12">
+    <row r="225" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A225" s="16" t="s">
         <v>37</v>
       </c>
@@ -9916,7 +9479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" ht="15" spans="1:12">
+    <row r="226" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A226" s="16" t="s">
         <v>37</v>
       </c>
@@ -9952,7 +9515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" ht="15" spans="1:12">
+    <row r="227" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A227" s="16" t="s">
         <v>37</v>
       </c>
@@ -9988,7 +9551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" ht="15" spans="1:12">
+    <row r="228" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A228" s="16" t="s">
         <v>37</v>
       </c>
@@ -10024,7 +9587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" ht="15" spans="1:12">
+    <row r="229" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A229" s="16" t="s">
         <v>131</v>
       </c>
@@ -10060,7 +9623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" ht="15" spans="1:12">
+    <row r="230" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A230" s="16" t="s">
         <v>132</v>
       </c>
@@ -10096,7 +9659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" ht="15" spans="1:12">
+    <row r="231" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A231" s="16" t="s">
         <v>133</v>
       </c>
@@ -10132,7 +9695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" ht="15" spans="1:12">
+    <row r="232" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A232" s="16" t="s">
         <v>134</v>
       </c>
@@ -10168,7 +9731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" ht="15" spans="1:12">
+    <row r="233" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A233" s="16" t="s">
         <v>135</v>
       </c>
@@ -10204,7 +9767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" ht="15" spans="1:12">
+    <row r="234" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A234" s="16" t="s">
         <v>136</v>
       </c>
@@ -10240,7 +9803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" ht="15" spans="1:12">
+    <row r="235" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A235" s="16" t="s">
         <v>137</v>
       </c>
@@ -10276,7 +9839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" ht="15" spans="1:12">
+    <row r="236" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A236" s="16" t="s">
         <v>37</v>
       </c>
@@ -10312,7 +9875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" ht="15" spans="1:12">
+    <row r="237" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A237" s="16" t="s">
         <v>138</v>
       </c>
@@ -10348,7 +9911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" ht="15" spans="1:12">
+    <row r="238" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A238" s="16" t="s">
         <v>139</v>
       </c>
@@ -10384,7 +9947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" ht="15" spans="1:12">
+    <row r="239" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A239" s="16" t="s">
         <v>140</v>
       </c>
@@ -10420,7 +9983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" ht="15" spans="1:12">
+    <row r="240" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A240" s="16" t="s">
         <v>141</v>
       </c>
@@ -10456,7 +10019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" ht="15" spans="1:12">
+    <row r="241" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A241" s="16" t="s">
         <v>37</v>
       </c>
@@ -10492,7 +10055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" ht="15" spans="1:12">
+    <row r="242" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A242" s="16" t="s">
         <v>37</v>
       </c>
@@ -10528,7 +10091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" ht="15" spans="1:12">
+    <row r="243" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A243" s="16" t="s">
         <v>37</v>
       </c>
@@ -10564,7 +10127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" ht="15" spans="1:12">
+    <row r="244" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A244" s="16" t="s">
         <v>37</v>
       </c>
@@ -10600,7 +10163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" ht="15" spans="1:12">
+    <row r="245" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A245" s="16" t="s">
         <v>46</v>
       </c>
@@ -10636,23 +10199,4727 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:12">
-      <c r="J246" s="25"/>
-    </row>
-    <row r="247" spans="1:12">
-      <c r="J247" s="25"/>
-    </row>
-    <row r="251" spans="1:12">
-      <c r="I251" s="20"/>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A246" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B246" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D246" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E246" s="3">
+        <v>0</v>
+      </c>
+      <c r="F246" s="4">
+        <v>0</v>
+      </c>
+      <c r="H246" s="19">
+        <v>1</v>
+      </c>
+      <c r="I246" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J246" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K246" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L246" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A247" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B247" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D247" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E247" s="3">
+        <v>1</v>
+      </c>
+      <c r="F247" s="16">
+        <v>0</v>
+      </c>
+      <c r="H247" s="19">
+        <v>1</v>
+      </c>
+      <c r="I247" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J247" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K247" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L247" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A248" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B248" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D248" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E248" s="3">
+        <v>1</v>
+      </c>
+      <c r="F248" s="16">
+        <v>1</v>
+      </c>
+      <c r="H248" s="19">
+        <v>1</v>
+      </c>
+      <c r="I248" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J248" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K248" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L248" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A249" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B249" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D249" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E249" s="3">
+        <v>1</v>
+      </c>
+      <c r="F249" s="16">
+        <v>2</v>
+      </c>
+      <c r="H249" s="19">
+        <v>1</v>
+      </c>
+      <c r="I249" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J249" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K249" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L249" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A250" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B250" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D250" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E250" s="3">
+        <v>1</v>
+      </c>
+      <c r="F250" s="16">
+        <v>3</v>
+      </c>
+      <c r="H250" s="19">
+        <v>1</v>
+      </c>
+      <c r="I250" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J250" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K250" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L250" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A251" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B251" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D251" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E251" s="3">
+        <v>1</v>
+      </c>
+      <c r="F251" s="16">
+        <v>4</v>
+      </c>
+      <c r="H251" s="19">
+        <v>1</v>
+      </c>
+      <c r="I251" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J251" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K251" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L251" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A252" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B252" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D252" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E252" s="3">
+        <v>1</v>
+      </c>
+      <c r="F252" s="16">
+        <v>5</v>
+      </c>
+      <c r="H252" s="19">
+        <v>1</v>
+      </c>
+      <c r="I252" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J252" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K252" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L252" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A253" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B253" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D253" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E253" s="3">
+        <v>1</v>
+      </c>
+      <c r="F253" s="16">
+        <v>6</v>
+      </c>
+      <c r="H253" s="19">
+        <v>1</v>
+      </c>
+      <c r="I253" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J253" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K253" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L253" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A254" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B254" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D254" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E254" s="3">
+        <v>1</v>
+      </c>
+      <c r="F254" s="16">
+        <v>7</v>
+      </c>
+      <c r="H254" s="19">
+        <v>1</v>
+      </c>
+      <c r="I254" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J254" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K254" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L254" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A255" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="B255" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D255" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E255" s="3">
+        <v>2</v>
+      </c>
+      <c r="F255" s="16">
+        <v>0</v>
+      </c>
+      <c r="H255" s="19">
+        <v>1</v>
+      </c>
+      <c r="I255" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J255" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K255" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L255" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A256" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B256" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D256" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E256" s="3">
+        <v>2</v>
+      </c>
+      <c r="F256" s="16">
+        <v>1</v>
+      </c>
+      <c r="H256" s="19">
+        <v>1</v>
+      </c>
+      <c r="I256" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J256" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K256" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L256" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A257" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B257" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D257" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E257" s="3">
+        <v>2</v>
+      </c>
+      <c r="F257" s="16">
+        <v>2</v>
+      </c>
+      <c r="H257" s="19">
+        <v>1</v>
+      </c>
+      <c r="I257" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J257" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K257" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L257" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A258" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B258" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D258" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E258" s="3">
+        <v>2</v>
+      </c>
+      <c r="F258" s="16">
+        <v>3</v>
+      </c>
+      <c r="H258" s="19">
+        <v>1</v>
+      </c>
+      <c r="I258" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J258" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K258" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L258" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A259" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B259" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D259" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E259" s="16">
+        <v>2</v>
+      </c>
+      <c r="F259" s="16">
+        <v>4</v>
+      </c>
+      <c r="H259" s="19">
+        <v>1</v>
+      </c>
+      <c r="I259" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J259" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K259" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L259" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A260" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B260" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D260" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E260" s="16">
+        <v>2</v>
+      </c>
+      <c r="F260" s="16">
+        <v>5</v>
+      </c>
+      <c r="H260" s="19">
+        <v>1</v>
+      </c>
+      <c r="I260" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J260" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K260" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L260" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A261" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B261" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D261" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E261" s="16">
+        <v>2</v>
+      </c>
+      <c r="F261" s="16">
+        <v>6</v>
+      </c>
+      <c r="H261" s="19">
+        <v>1</v>
+      </c>
+      <c r="I261" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J261" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K261" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L261" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A262" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B262" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D262" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E262" s="16">
+        <v>2</v>
+      </c>
+      <c r="F262" s="16">
+        <v>7</v>
+      </c>
+      <c r="H262" s="19">
+        <v>1</v>
+      </c>
+      <c r="I262" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J262" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K262" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L262" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A263" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B263" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D263" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E263" s="16">
+        <v>3</v>
+      </c>
+      <c r="F263" s="16">
+        <v>0</v>
+      </c>
+      <c r="H263" s="19">
+        <v>1</v>
+      </c>
+      <c r="I263" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J263" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K263" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L263" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A264" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B264" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D264" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E264" s="16">
+        <v>3</v>
+      </c>
+      <c r="F264" s="16">
+        <v>1</v>
+      </c>
+      <c r="H264" s="19">
+        <v>1</v>
+      </c>
+      <c r="I264" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J264" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K264" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L264" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A265" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B265" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D265" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E265" s="16">
+        <v>3</v>
+      </c>
+      <c r="F265" s="16">
+        <v>2</v>
+      </c>
+      <c r="H265" s="19">
+        <v>1</v>
+      </c>
+      <c r="I265" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J265" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K265" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L265" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A266" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B266" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D266" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E266" s="16">
+        <v>3</v>
+      </c>
+      <c r="F266" s="16">
+        <v>3</v>
+      </c>
+      <c r="H266" s="19">
+        <v>1</v>
+      </c>
+      <c r="I266" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J266" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K266" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L266" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A267" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B267" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D267" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E267" s="16">
+        <v>3</v>
+      </c>
+      <c r="F267" s="16">
+        <v>4</v>
+      </c>
+      <c r="H267" s="19">
+        <v>1</v>
+      </c>
+      <c r="I267" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J267" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K267" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L267" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A268" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B268" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D268" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E268" s="16">
+        <v>3</v>
+      </c>
+      <c r="F268" s="16">
+        <v>5</v>
+      </c>
+      <c r="H268" s="19">
+        <v>1</v>
+      </c>
+      <c r="I268" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J268" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K268" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L268" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A269" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B269" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D269" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E269" s="16">
+        <v>3</v>
+      </c>
+      <c r="F269" s="16">
+        <v>6</v>
+      </c>
+      <c r="H269" s="19">
+        <v>1</v>
+      </c>
+      <c r="I269" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J269" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K269" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L269" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A270" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B270" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D270" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E270" s="16">
+        <v>3</v>
+      </c>
+      <c r="F270" s="16">
+        <v>7</v>
+      </c>
+      <c r="H270" s="19">
+        <v>1</v>
+      </c>
+      <c r="I270" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J270" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K270" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L270" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A271" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B271" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D271" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E271" s="16">
+        <v>4</v>
+      </c>
+      <c r="F271" s="16">
+        <v>0</v>
+      </c>
+      <c r="H271" s="19">
+        <v>1</v>
+      </c>
+      <c r="I271" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J271" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K271" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L271" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A272" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B272" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D272" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E272" s="16">
+        <v>6</v>
+      </c>
+      <c r="F272" s="16">
+        <v>0</v>
+      </c>
+      <c r="H272" s="19">
+        <v>1</v>
+      </c>
+      <c r="I272" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J272" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K272" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L272" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A273" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="B273" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D273" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E273" s="16">
+        <v>8</v>
+      </c>
+      <c r="F273" s="16">
+        <v>0</v>
+      </c>
+      <c r="H273" s="19">
+        <v>1</v>
+      </c>
+      <c r="I273" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J273" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K273" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L273" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A274" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B274" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D274" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E274" s="16">
+        <v>10</v>
+      </c>
+      <c r="F274" s="16">
+        <v>0</v>
+      </c>
+      <c r="H274" s="19">
+        <v>1</v>
+      </c>
+      <c r="I274" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J274" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K274" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L274" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A275" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B275" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D275" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E275" s="16">
+        <v>12</v>
+      </c>
+      <c r="F275" s="16">
+        <v>0</v>
+      </c>
+      <c r="H275" s="19">
+        <v>1</v>
+      </c>
+      <c r="I275" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J275" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K275" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L275" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A276" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B276" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D276" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E276" s="16">
+        <v>14</v>
+      </c>
+      <c r="F276" s="16">
+        <v>0</v>
+      </c>
+      <c r="H276" s="19">
+        <v>1</v>
+      </c>
+      <c r="I276" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J276" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K276" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L276" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A277" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B277" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D277" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E277" s="16">
+        <v>16</v>
+      </c>
+      <c r="F277" s="16">
+        <v>0</v>
+      </c>
+      <c r="H277" s="19">
+        <v>1</v>
+      </c>
+      <c r="I277" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J277" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K277" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L277" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A278" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B278" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C278" s="16"/>
+      <c r="D278" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E278" s="16">
+        <v>16</v>
+      </c>
+      <c r="F278" s="16">
+        <v>1</v>
+      </c>
+      <c r="H278" s="19">
+        <v>1</v>
+      </c>
+      <c r="I278" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J278" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K278" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L278" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A279" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B279" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C279" s="16"/>
+      <c r="D279" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E279" s="16">
+        <v>16</v>
+      </c>
+      <c r="F279" s="16">
+        <v>2</v>
+      </c>
+      <c r="H279" s="19">
+        <v>1</v>
+      </c>
+      <c r="I279" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J279" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K279" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L279" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A280" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B280" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C280" s="16"/>
+      <c r="D280" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E280" s="16">
+        <v>16</v>
+      </c>
+      <c r="F280" s="16">
+        <v>3</v>
+      </c>
+      <c r="H280" s="19">
+        <v>1</v>
+      </c>
+      <c r="I280" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J280" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K280" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L280" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A281" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B281" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C281" s="16"/>
+      <c r="D281" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E281" s="16">
+        <v>16</v>
+      </c>
+      <c r="F281" s="16">
+        <v>4</v>
+      </c>
+      <c r="H281" s="19">
+        <v>1</v>
+      </c>
+      <c r="I281" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J281" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K281" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L281" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A282" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="B282" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C282" s="16"/>
+      <c r="D282" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E282" s="16">
+        <v>16</v>
+      </c>
+      <c r="F282" s="16">
+        <v>5</v>
+      </c>
+      <c r="H282" s="19">
+        <v>1</v>
+      </c>
+      <c r="I282" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J282" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K282" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L282" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A283" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="B283" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C283" s="16"/>
+      <c r="D283" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E283" s="16">
+        <v>16</v>
+      </c>
+      <c r="F283" s="16">
+        <v>6</v>
+      </c>
+      <c r="H283" s="19">
+        <v>1</v>
+      </c>
+      <c r="I283" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J283" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K283" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L283" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A284" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="B284" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C284" s="16"/>
+      <c r="D284" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E284" s="16">
+        <v>16</v>
+      </c>
+      <c r="F284" s="16">
+        <v>7</v>
+      </c>
+      <c r="H284" s="19">
+        <v>1</v>
+      </c>
+      <c r="I284" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J284" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K284" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L284" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A285" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B285" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C285" s="16"/>
+      <c r="D285" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E285" s="16">
+        <v>17</v>
+      </c>
+      <c r="F285" s="16">
+        <v>0</v>
+      </c>
+      <c r="H285" s="19">
+        <v>1</v>
+      </c>
+      <c r="I285" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J285" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K285" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L285" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A286" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B286" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C286" s="16"/>
+      <c r="D286" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E286" s="16">
+        <v>17</v>
+      </c>
+      <c r="F286" s="16">
+        <v>1</v>
+      </c>
+      <c r="H286" s="19">
+        <v>1</v>
+      </c>
+      <c r="I286" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J286" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K286" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L286" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A287" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="B287" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D287" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E287" s="16">
+        <v>17</v>
+      </c>
+      <c r="F287" s="16">
+        <v>2</v>
+      </c>
+      <c r="H287" s="19">
+        <v>1</v>
+      </c>
+      <c r="I287" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J287" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K287" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L287" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A288" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="B288" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D288" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E288" s="16">
+        <v>17</v>
+      </c>
+      <c r="F288" s="16">
+        <v>3</v>
+      </c>
+      <c r="H288" s="19">
+        <v>1</v>
+      </c>
+      <c r="I288" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J288" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K288" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L288" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A289" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="B289" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D289" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E289" s="16">
+        <v>17</v>
+      </c>
+      <c r="F289" s="16">
+        <v>4</v>
+      </c>
+      <c r="H289" s="19">
+        <v>1</v>
+      </c>
+      <c r="I289" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J289" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K289" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L289" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A290" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="B290" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D290" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E290" s="16">
+        <v>17</v>
+      </c>
+      <c r="F290" s="16">
+        <v>5</v>
+      </c>
+      <c r="H290" s="19">
+        <v>1</v>
+      </c>
+      <c r="I290" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J290" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K290" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L290" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A291" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B291" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D291" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E291" s="16">
+        <v>17</v>
+      </c>
+      <c r="F291" s="16">
+        <v>6</v>
+      </c>
+      <c r="H291" s="19">
+        <v>1</v>
+      </c>
+      <c r="I291" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J291" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K291" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L291" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A292" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B292" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D292" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E292" s="16">
+        <v>17</v>
+      </c>
+      <c r="F292" s="16">
+        <v>7</v>
+      </c>
+      <c r="H292" s="19">
+        <v>1</v>
+      </c>
+      <c r="I292" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J292" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K292" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L292" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A293" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="B293" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D293" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E293" s="3">
+        <v>18</v>
+      </c>
+      <c r="F293" s="4">
+        <v>0</v>
+      </c>
+      <c r="H293" s="19">
+        <v>1</v>
+      </c>
+      <c r="I293" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J293" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K293" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L293" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A294" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B294" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D294" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E294" s="3">
+        <v>20</v>
+      </c>
+      <c r="F294" s="4">
+        <v>0</v>
+      </c>
+      <c r="H294" s="19">
+        <v>1</v>
+      </c>
+      <c r="I294" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J294" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K294" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L294" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A295" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="B295" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D295" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E295" s="3">
+        <v>22</v>
+      </c>
+      <c r="F295" s="4">
+        <v>0</v>
+      </c>
+      <c r="H295" s="19">
+        <v>1</v>
+      </c>
+      <c r="I295" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J295" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K295" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L295" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A296" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B296" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D296" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E296" s="3">
+        <v>24</v>
+      </c>
+      <c r="F296" s="16">
+        <v>0</v>
+      </c>
+      <c r="H296" s="19">
+        <v>1</v>
+      </c>
+      <c r="I296" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J296" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K296" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L296" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A297" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B297" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D297" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E297" s="3">
+        <v>24</v>
+      </c>
+      <c r="F297" s="16">
+        <v>1</v>
+      </c>
+      <c r="H297" s="19">
+        <v>1</v>
+      </c>
+      <c r="I297" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J297" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K297" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L297" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A298" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B298" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D298" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E298" s="3">
+        <v>24</v>
+      </c>
+      <c r="F298" s="16">
+        <v>2</v>
+      </c>
+      <c r="H298" s="19">
+        <v>1</v>
+      </c>
+      <c r="I298" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J298" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K298" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L298" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A299" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="B299" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D299" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E299" s="3">
+        <v>24</v>
+      </c>
+      <c r="F299" s="16">
+        <v>3</v>
+      </c>
+      <c r="H299" s="19">
+        <v>1</v>
+      </c>
+      <c r="I299" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J299" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K299" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L299" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A300" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B300" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D300" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E300" s="3">
+        <v>24</v>
+      </c>
+      <c r="F300" s="16">
+        <v>4</v>
+      </c>
+      <c r="H300" s="19">
+        <v>1</v>
+      </c>
+      <c r="I300" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J300" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K300" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L300" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A301" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B301" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D301" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E301" s="3">
+        <v>24</v>
+      </c>
+      <c r="F301" s="16">
+        <v>5</v>
+      </c>
+      <c r="H301" s="19">
+        <v>1</v>
+      </c>
+      <c r="I301" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J301" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K301" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L301" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A302" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B302" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D302" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E302" s="3">
+        <v>24</v>
+      </c>
+      <c r="F302" s="16">
+        <v>6</v>
+      </c>
+      <c r="H302" s="19">
+        <v>1</v>
+      </c>
+      <c r="I302" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J302" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K302" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L302" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A303" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B303" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D303" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E303" s="3">
+        <v>24</v>
+      </c>
+      <c r="F303" s="16">
+        <v>7</v>
+      </c>
+      <c r="H303" s="19">
+        <v>1</v>
+      </c>
+      <c r="I303" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J303" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K303" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L303" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A304" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B304" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D304" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E304" s="3">
+        <v>25</v>
+      </c>
+      <c r="F304" s="4">
+        <v>0</v>
+      </c>
+      <c r="H304" s="19">
+        <v>1</v>
+      </c>
+      <c r="I304" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J304" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K304" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L304" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A305" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B305" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D305" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E305" s="3">
+        <v>26</v>
+      </c>
+      <c r="F305" s="4">
+        <v>0</v>
+      </c>
+      <c r="H305" s="19">
+        <v>1</v>
+      </c>
+      <c r="I305" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J305" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K305" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L305" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A306" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B306" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D306" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E306" s="3">
+        <v>30</v>
+      </c>
+      <c r="F306" s="4">
+        <v>0</v>
+      </c>
+      <c r="H306" s="19">
+        <v>1</v>
+      </c>
+      <c r="I306" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J306" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K306" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L306" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A307" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B307" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D307" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E307" s="3">
+        <v>0</v>
+      </c>
+      <c r="F307" s="4">
+        <v>0</v>
+      </c>
+      <c r="H307" s="19">
+        <v>1</v>
+      </c>
+      <c r="I307" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J307" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K307" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L307" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A308" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B308" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D308" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E308" s="3">
+        <v>1</v>
+      </c>
+      <c r="F308" s="4">
+        <v>0</v>
+      </c>
+      <c r="H308" s="19">
+        <v>1</v>
+      </c>
+      <c r="I308" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J308" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K308" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L308" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A309" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B309" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D309" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E309" s="3">
+        <v>2</v>
+      </c>
+      <c r="F309" s="4">
+        <v>0</v>
+      </c>
+      <c r="H309" s="19">
+        <v>1</v>
+      </c>
+      <c r="I309" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J309" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K309" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L309" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A310" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B310" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D310" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E310" s="3">
+        <v>4</v>
+      </c>
+      <c r="F310" s="4">
+        <v>0</v>
+      </c>
+      <c r="H310" s="19">
+        <v>1</v>
+      </c>
+      <c r="I310" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J310" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K310" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L310" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A311" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B311" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D311" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E311" s="3">
+        <v>5</v>
+      </c>
+      <c r="F311" s="16">
+        <v>0</v>
+      </c>
+      <c r="H311" s="19">
+        <v>1</v>
+      </c>
+      <c r="I311" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J311" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K311" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L311" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A312" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B312" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D312" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E312" s="3">
+        <v>5</v>
+      </c>
+      <c r="F312" s="16">
+        <v>1</v>
+      </c>
+      <c r="H312" s="19">
+        <v>1</v>
+      </c>
+      <c r="I312" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J312" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K312" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L312" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A313" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B313" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D313" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E313" s="3">
+        <v>5</v>
+      </c>
+      <c r="F313" s="16">
+        <v>2</v>
+      </c>
+      <c r="H313" s="19">
+        <v>1</v>
+      </c>
+      <c r="I313" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J313" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K313" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L313" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A314" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B314" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D314" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E314" s="3">
+        <v>5</v>
+      </c>
+      <c r="F314" s="16">
+        <v>3</v>
+      </c>
+      <c r="H314" s="19">
+        <v>1</v>
+      </c>
+      <c r="I314" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J314" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K314" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L314" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A315" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B315" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D315" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E315" s="3">
+        <v>5</v>
+      </c>
+      <c r="F315" s="16">
+        <v>4</v>
+      </c>
+      <c r="H315" s="19">
+        <v>1</v>
+      </c>
+      <c r="I315" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J315" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K315" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L315" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A316" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B316" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D316" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E316" s="3">
+        <v>5</v>
+      </c>
+      <c r="F316" s="16">
+        <v>5</v>
+      </c>
+      <c r="H316" s="19">
+        <v>1</v>
+      </c>
+      <c r="I316" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J316" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K316" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L316" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A317" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B317" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D317" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E317" s="3">
+        <v>5</v>
+      </c>
+      <c r="F317" s="16">
+        <v>6</v>
+      </c>
+      <c r="H317" s="19">
+        <v>1</v>
+      </c>
+      <c r="I317" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J317" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K317" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L317" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A318" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B318" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D318" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E318" s="3">
+        <v>5</v>
+      </c>
+      <c r="F318" s="16">
+        <v>7</v>
+      </c>
+      <c r="H318" s="19">
+        <v>1</v>
+      </c>
+      <c r="I318" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J318" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K318" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L318" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A319" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B319" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D319" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E319" s="3">
+        <v>6</v>
+      </c>
+      <c r="F319" s="4">
+        <v>0</v>
+      </c>
+      <c r="H319" s="19">
+        <v>1</v>
+      </c>
+      <c r="I319" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J319" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K319" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L319" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A320" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="B320" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D320" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E320" s="3">
+        <v>8</v>
+      </c>
+      <c r="F320" s="4">
+        <v>0</v>
+      </c>
+      <c r="H320" s="19">
+        <v>1</v>
+      </c>
+      <c r="I320" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J320" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K320" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L320" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A321" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B321" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D321" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E321" s="3">
+        <v>10</v>
+      </c>
+      <c r="F321" s="4">
+        <v>0</v>
+      </c>
+      <c r="H321" s="19">
+        <v>1</v>
+      </c>
+      <c r="I321" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J321" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K321" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L321" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A322" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B322" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D322" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E322" s="3">
+        <v>14</v>
+      </c>
+      <c r="F322" s="16">
+        <v>0</v>
+      </c>
+      <c r="H322" s="19">
+        <v>1</v>
+      </c>
+      <c r="I322" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J322" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K322" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L322" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A323" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B323" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D323" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E323" s="3">
+        <v>14</v>
+      </c>
+      <c r="F323" s="16">
+        <v>1</v>
+      </c>
+      <c r="H323" s="19">
+        <v>1</v>
+      </c>
+      <c r="I323" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J323" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K323" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L323" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A324" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B324" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D324" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E324" s="3">
+        <v>14</v>
+      </c>
+      <c r="F324" s="16">
+        <v>2</v>
+      </c>
+      <c r="H324" s="19">
+        <v>1</v>
+      </c>
+      <c r="I324" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J324" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K324" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L324" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A325" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B325" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D325" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E325" s="3">
+        <v>14</v>
+      </c>
+      <c r="F325" s="16">
+        <v>3</v>
+      </c>
+      <c r="H325" s="19">
+        <v>1</v>
+      </c>
+      <c r="I325" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J325" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K325" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L325" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A326" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B326" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D326" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E326" s="3">
+        <v>14</v>
+      </c>
+      <c r="F326" s="16">
+        <v>4</v>
+      </c>
+      <c r="H326" s="19">
+        <v>1</v>
+      </c>
+      <c r="I326" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J326" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K326" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L326" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A327" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B327" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D327" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E327" s="3">
+        <v>14</v>
+      </c>
+      <c r="F327" s="16">
+        <v>5</v>
+      </c>
+      <c r="H327" s="19">
+        <v>1</v>
+      </c>
+      <c r="I327" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J327" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K327" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L327" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A328" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B328" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D328" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E328" s="3">
+        <v>14</v>
+      </c>
+      <c r="F328" s="16">
+        <v>6</v>
+      </c>
+      <c r="H328" s="19">
+        <v>1</v>
+      </c>
+      <c r="I328" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J328" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K328" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L328" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A329" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B329" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D329" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E329" s="3">
+        <v>14</v>
+      </c>
+      <c r="F329" s="16">
+        <v>7</v>
+      </c>
+      <c r="H329" s="19">
+        <v>1</v>
+      </c>
+      <c r="I329" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J329" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K329" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L329" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A330" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B330" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D330" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E330" s="3">
+        <v>15</v>
+      </c>
+      <c r="F330" s="16">
+        <v>0</v>
+      </c>
+      <c r="H330" s="19">
+        <v>1</v>
+      </c>
+      <c r="I330" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J330" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K330" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L330" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A331" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B331" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D331" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E331" s="3">
+        <v>15</v>
+      </c>
+      <c r="F331" s="16">
+        <v>1</v>
+      </c>
+      <c r="H331" s="19">
+        <v>1</v>
+      </c>
+      <c r="I331" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J331" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K331" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L331" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A332" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B332" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D332" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E332" s="3">
+        <v>15</v>
+      </c>
+      <c r="F332" s="16">
+        <v>2</v>
+      </c>
+      <c r="H332" s="19">
+        <v>1</v>
+      </c>
+      <c r="I332" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J332" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K332" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L332" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A333" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B333" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D333" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E333" s="3">
+        <v>15</v>
+      </c>
+      <c r="F333" s="16">
+        <v>3</v>
+      </c>
+      <c r="H333" s="19">
+        <v>1</v>
+      </c>
+      <c r="I333" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J333" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K333" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L333" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A334" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B334" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D334" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E334" s="3">
+        <v>15</v>
+      </c>
+      <c r="F334" s="16">
+        <v>4</v>
+      </c>
+      <c r="H334" s="19">
+        <v>1</v>
+      </c>
+      <c r="I334" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J334" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K334" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L334" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A335" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B335" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D335" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E335" s="3">
+        <v>15</v>
+      </c>
+      <c r="F335" s="16">
+        <v>5</v>
+      </c>
+      <c r="H335" s="19">
+        <v>1</v>
+      </c>
+      <c r="I335" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J335" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K335" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L335" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A336" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B336" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D336" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E336" s="3">
+        <v>15</v>
+      </c>
+      <c r="F336" s="16">
+        <v>6</v>
+      </c>
+      <c r="H336" s="19">
+        <v>1</v>
+      </c>
+      <c r="I336" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J336" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K336" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L336" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A337" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B337" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D337" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E337" s="3">
+        <v>15</v>
+      </c>
+      <c r="F337" s="16">
+        <v>7</v>
+      </c>
+      <c r="H337" s="19">
+        <v>1</v>
+      </c>
+      <c r="I337" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J337" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K337" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L337" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A338" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B338" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D338" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E338" s="3">
+        <v>16</v>
+      </c>
+      <c r="F338" s="4">
+        <v>0</v>
+      </c>
+      <c r="H338" s="19">
+        <v>1</v>
+      </c>
+      <c r="I338" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J338" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K338" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L338" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A339" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B339" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D339" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E339" s="3">
+        <v>20</v>
+      </c>
+      <c r="F339" s="4">
+        <v>0</v>
+      </c>
+      <c r="H339" s="19">
+        <v>1</v>
+      </c>
+      <c r="I339" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J339" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K339" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L339" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A340" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B340" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D340" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E340" s="3">
+        <v>24</v>
+      </c>
+      <c r="F340" s="4">
+        <v>0</v>
+      </c>
+      <c r="H340" s="19">
+        <v>1</v>
+      </c>
+      <c r="I340" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J340" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K340" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L340" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A341" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B341" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D341" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E341" s="3">
+        <v>28</v>
+      </c>
+      <c r="F341" s="16">
+        <v>0</v>
+      </c>
+      <c r="H341" s="19">
+        <v>1</v>
+      </c>
+      <c r="I341" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J341" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K341" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L341" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A342" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B342" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D342" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E342" s="3">
+        <v>28</v>
+      </c>
+      <c r="F342" s="16">
+        <v>1</v>
+      </c>
+      <c r="H342" s="19">
+        <v>1</v>
+      </c>
+      <c r="I342" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J342" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K342" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L342" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A343" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="B343" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D343" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E343" s="3">
+        <v>28</v>
+      </c>
+      <c r="F343" s="16">
+        <v>3</v>
+      </c>
+      <c r="H343" s="19">
+        <v>1</v>
+      </c>
+      <c r="I343" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J343" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K343" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L343" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A344" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B344" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D344" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E344" s="3">
+        <v>28</v>
+      </c>
+      <c r="F344" s="16">
+        <v>4</v>
+      </c>
+      <c r="H344" s="19">
+        <v>1</v>
+      </c>
+      <c r="I344" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J344" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K344" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L344" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A345" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B345" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D345" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E345" s="3">
+        <v>28</v>
+      </c>
+      <c r="F345" s="16">
+        <v>5</v>
+      </c>
+      <c r="H345" s="19">
+        <v>1</v>
+      </c>
+      <c r="I345" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J345" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K345" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L345" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A346" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B346" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D346" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E346" s="3">
+        <v>28</v>
+      </c>
+      <c r="F346" s="16">
+        <v>6</v>
+      </c>
+      <c r="H346" s="19">
+        <v>1</v>
+      </c>
+      <c r="I346" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J346" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K346" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L346" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A347" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B347" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D347" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E347" s="3">
+        <v>28</v>
+      </c>
+      <c r="F347" s="16">
+        <v>7</v>
+      </c>
+      <c r="H347" s="19">
+        <v>1</v>
+      </c>
+      <c r="I347" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J347" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K347" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L347" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A348" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B348" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D348" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E348" s="3">
+        <v>29</v>
+      </c>
+      <c r="F348" s="16">
+        <v>0</v>
+      </c>
+      <c r="H348" s="19">
+        <v>1</v>
+      </c>
+      <c r="I348" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J348" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K348" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L348" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A349" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B349" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D349" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E349" s="3">
+        <v>30</v>
+      </c>
+      <c r="F349" s="4">
+        <v>0</v>
+      </c>
+      <c r="H349" s="19">
+        <v>1</v>
+      </c>
+      <c r="I349" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J349" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K349" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L349" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A350" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B350" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D350" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E350" s="3">
+        <v>0</v>
+      </c>
+      <c r="F350" s="4">
+        <v>0</v>
+      </c>
+      <c r="H350" s="19">
+        <v>1</v>
+      </c>
+      <c r="I350" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J350" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K350" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L350" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A351" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B351" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D351" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E351" s="3">
+        <v>1</v>
+      </c>
+      <c r="F351" s="4">
+        <v>0</v>
+      </c>
+      <c r="H351" s="19">
+        <v>1</v>
+      </c>
+      <c r="I351" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J351" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K351" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L351" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A352" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B352" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D352" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E352" s="3">
+        <v>2</v>
+      </c>
+      <c r="F352" s="4">
+        <v>0</v>
+      </c>
+      <c r="H352" s="19">
+        <v>1</v>
+      </c>
+      <c r="I352" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J352" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K352" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L352" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A353" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B353" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D353" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E353" s="3">
+        <v>4</v>
+      </c>
+      <c r="F353" s="4">
+        <v>0</v>
+      </c>
+      <c r="H353" s="19">
+        <v>1</v>
+      </c>
+      <c r="I353" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J353" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K353" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L353" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A354" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B354" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D354" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E354" s="3">
+        <v>5</v>
+      </c>
+      <c r="F354" s="16">
+        <v>0</v>
+      </c>
+      <c r="H354" s="19">
+        <v>1</v>
+      </c>
+      <c r="I354" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J354" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K354" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L354" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A355" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B355" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D355" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E355" s="3">
+        <v>5</v>
+      </c>
+      <c r="F355" s="16">
+        <v>1</v>
+      </c>
+      <c r="H355" s="19">
+        <v>1</v>
+      </c>
+      <c r="I355" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J355" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K355" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L355" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A356" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B356" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D356" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E356" s="3">
+        <v>5</v>
+      </c>
+      <c r="F356" s="16">
+        <v>2</v>
+      </c>
+      <c r="H356" s="19">
+        <v>1</v>
+      </c>
+      <c r="I356" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J356" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K356" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L356" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A357" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B357" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D357" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E357" s="3">
+        <v>5</v>
+      </c>
+      <c r="F357" s="16">
+        <v>3</v>
+      </c>
+      <c r="H357" s="19">
+        <v>1</v>
+      </c>
+      <c r="I357" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J357" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K357" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L357" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A358" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B358" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D358" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E358" s="3">
+        <v>5</v>
+      </c>
+      <c r="F358" s="16">
+        <v>4</v>
+      </c>
+      <c r="H358" s="19">
+        <v>1</v>
+      </c>
+      <c r="I358" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J358" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K358" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L358" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A359" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B359" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D359" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E359" s="3">
+        <v>5</v>
+      </c>
+      <c r="F359" s="16">
+        <v>5</v>
+      </c>
+      <c r="H359" s="19">
+        <v>1</v>
+      </c>
+      <c r="I359" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J359" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K359" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L359" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A360" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B360" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D360" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E360" s="3">
+        <v>5</v>
+      </c>
+      <c r="F360" s="16">
+        <v>6</v>
+      </c>
+      <c r="H360" s="19">
+        <v>1</v>
+      </c>
+      <c r="I360" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J360" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K360" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L360" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A361" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B361" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D361" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E361" s="3">
+        <v>5</v>
+      </c>
+      <c r="F361" s="16">
+        <v>7</v>
+      </c>
+      <c r="H361" s="19">
+        <v>1</v>
+      </c>
+      <c r="I361" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J361" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K361" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L361" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A362" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B362" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D362" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E362" s="3">
+        <v>6</v>
+      </c>
+      <c r="F362" s="4">
+        <v>0</v>
+      </c>
+      <c r="H362" s="19">
+        <v>1</v>
+      </c>
+      <c r="I362" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J362" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K362" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L362" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A363" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="B363" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D363" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E363" s="3">
+        <v>8</v>
+      </c>
+      <c r="F363" s="4">
+        <v>0</v>
+      </c>
+      <c r="H363" s="19">
+        <v>1</v>
+      </c>
+      <c r="I363" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J363" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K363" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L363" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A364" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B364" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D364" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E364" s="3">
+        <v>10</v>
+      </c>
+      <c r="F364" s="4">
+        <v>0</v>
+      </c>
+      <c r="H364" s="19">
+        <v>1</v>
+      </c>
+      <c r="I364" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J364" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K364" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L364" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A365" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B365" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D365" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E365" s="3">
+        <v>14</v>
+      </c>
+      <c r="F365" s="16">
+        <v>0</v>
+      </c>
+      <c r="H365" s="19">
+        <v>1</v>
+      </c>
+      <c r="I365" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J365" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K365" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L365" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A366" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B366" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D366" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E366" s="3">
+        <v>14</v>
+      </c>
+      <c r="F366" s="16">
+        <v>1</v>
+      </c>
+      <c r="H366" s="19">
+        <v>1</v>
+      </c>
+      <c r="I366" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J366" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K366" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L366" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A367" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B367" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D367" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E367" s="3">
+        <v>14</v>
+      </c>
+      <c r="F367" s="16">
+        <v>2</v>
+      </c>
+      <c r="H367" s="19">
+        <v>1</v>
+      </c>
+      <c r="I367" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J367" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K367" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L367" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A368" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B368" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D368" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E368" s="3">
+        <v>14</v>
+      </c>
+      <c r="F368" s="16">
+        <v>3</v>
+      </c>
+      <c r="H368" s="19">
+        <v>1</v>
+      </c>
+      <c r="I368" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J368" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K368" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L368" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A369" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B369" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D369" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E369" s="3">
+        <v>14</v>
+      </c>
+      <c r="F369" s="16">
+        <v>4</v>
+      </c>
+      <c r="H369" s="19">
+        <v>1</v>
+      </c>
+      <c r="I369" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J369" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K369" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L369" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A370" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B370" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D370" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E370" s="3">
+        <v>14</v>
+      </c>
+      <c r="F370" s="16">
+        <v>5</v>
+      </c>
+      <c r="H370" s="19">
+        <v>1</v>
+      </c>
+      <c r="I370" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J370" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K370" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L370" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A371" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B371" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D371" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E371" s="3">
+        <v>14</v>
+      </c>
+      <c r="F371" s="16">
+        <v>6</v>
+      </c>
+      <c r="H371" s="19">
+        <v>1</v>
+      </c>
+      <c r="I371" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J371" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K371" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L371" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A372" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B372" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D372" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E372" s="3">
+        <v>14</v>
+      </c>
+      <c r="F372" s="16">
+        <v>7</v>
+      </c>
+      <c r="H372" s="19">
+        <v>1</v>
+      </c>
+      <c r="I372" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J372" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K372" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L372" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A373" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B373" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D373" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E373" s="3">
+        <v>15</v>
+      </c>
+      <c r="F373" s="16">
+        <v>0</v>
+      </c>
+      <c r="H373" s="19">
+        <v>1</v>
+      </c>
+      <c r="I373" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J373" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K373" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L373" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A374" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B374" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D374" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E374" s="3">
+        <v>15</v>
+      </c>
+      <c r="F374" s="16">
+        <v>1</v>
+      </c>
+      <c r="H374" s="19">
+        <v>1</v>
+      </c>
+      <c r="I374" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J374" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K374" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L374" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A375" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B375" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D375" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E375" s="3">
+        <v>15</v>
+      </c>
+      <c r="F375" s="16">
+        <v>2</v>
+      </c>
+      <c r="H375" s="19">
+        <v>1</v>
+      </c>
+      <c r="I375" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J375" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K375" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L375" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A376" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B376" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D376" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E376" s="3">
+        <v>15</v>
+      </c>
+      <c r="F376" s="16">
+        <v>3</v>
+      </c>
+      <c r="H376" s="19">
+        <v>1</v>
+      </c>
+      <c r="I376" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J376" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K376" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L376" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A377" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B377" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D377" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E377" s="3">
+        <v>15</v>
+      </c>
+      <c r="F377" s="16">
+        <v>4</v>
+      </c>
+      <c r="H377" s="19">
+        <v>1</v>
+      </c>
+      <c r="I377" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J377" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K377" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L377" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A378" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B378" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D378" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E378" s="3">
+        <v>15</v>
+      </c>
+      <c r="F378" s="16">
+        <v>5</v>
+      </c>
+      <c r="H378" s="19">
+        <v>1</v>
+      </c>
+      <c r="I378" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J378" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K378" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L378" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A379" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B379" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D379" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E379" s="3">
+        <v>15</v>
+      </c>
+      <c r="F379" s="16">
+        <v>6</v>
+      </c>
+      <c r="H379" s="19">
+        <v>1</v>
+      </c>
+      <c r="I379" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J379" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K379" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L379" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A380" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B380" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D380" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E380" s="3">
+        <v>15</v>
+      </c>
+      <c r="F380" s="16">
+        <v>7</v>
+      </c>
+      <c r="H380" s="19">
+        <v>1</v>
+      </c>
+      <c r="I380" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J380" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K380" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L380" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A381" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B381" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D381" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E381" s="3">
+        <v>16</v>
+      </c>
+      <c r="F381" s="4">
+        <v>0</v>
+      </c>
+      <c r="H381" s="19">
+        <v>1</v>
+      </c>
+      <c r="I381" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J381" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K381" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L381" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A382" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B382" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D382" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E382" s="3">
+        <v>20</v>
+      </c>
+      <c r="F382" s="4">
+        <v>0</v>
+      </c>
+      <c r="H382" s="19">
+        <v>1</v>
+      </c>
+      <c r="I382" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J382" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K382" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L382" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A383" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B383" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D383" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E383" s="3">
+        <v>24</v>
+      </c>
+      <c r="F383" s="4">
+        <v>0</v>
+      </c>
+      <c r="H383" s="19">
+        <v>1</v>
+      </c>
+      <c r="I383" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J383" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K383" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L383" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A384" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B384" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D384" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E384" s="3">
+        <v>28</v>
+      </c>
+      <c r="F384" s="16">
+        <v>0</v>
+      </c>
+      <c r="H384" s="19">
+        <v>1</v>
+      </c>
+      <c r="I384" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J384" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K384" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L384" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A385" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B385" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D385" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E385" s="3">
+        <v>28</v>
+      </c>
+      <c r="F385" s="16">
+        <v>1</v>
+      </c>
+      <c r="H385" s="19">
+        <v>1</v>
+      </c>
+      <c r="I385" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J385" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K385" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L385" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A386" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="B386" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D386" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E386" s="3">
+        <v>28</v>
+      </c>
+      <c r="F386" s="16">
+        <v>3</v>
+      </c>
+      <c r="H386" s="19">
+        <v>1</v>
+      </c>
+      <c r="I386" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J386" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K386" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L386" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A387" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B387" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D387" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E387" s="3">
+        <v>28</v>
+      </c>
+      <c r="F387" s="16">
+        <v>4</v>
+      </c>
+      <c r="H387" s="19">
+        <v>1</v>
+      </c>
+      <c r="I387" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J387" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K387" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L387" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A388" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B388" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D388" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E388" s="3">
+        <v>28</v>
+      </c>
+      <c r="F388" s="16">
+        <v>5</v>
+      </c>
+      <c r="H388" s="19">
+        <v>1</v>
+      </c>
+      <c r="I388" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J388" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K388" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L388" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A389" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B389" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D389" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E389" s="3">
+        <v>28</v>
+      </c>
+      <c r="F389" s="16">
+        <v>6</v>
+      </c>
+      <c r="H389" s="19">
+        <v>1</v>
+      </c>
+      <c r="I389" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J389" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K389" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L389" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A390" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B390" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D390" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E390" s="3">
+        <v>28</v>
+      </c>
+      <c r="F390" s="16">
+        <v>7</v>
+      </c>
+      <c r="H390" s="19">
+        <v>1</v>
+      </c>
+      <c r="I390" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J390" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K390" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L390" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A391" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B391" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D391" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E391" s="3">
+        <v>29</v>
+      </c>
+      <c r="F391" s="16">
+        <v>0</v>
+      </c>
+      <c r="H391" s="19">
+        <v>1</v>
+      </c>
+      <c r="I391" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J391" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K391" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L391" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A392" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B392" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D392" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E392" s="3">
+        <v>30</v>
+      </c>
+      <c r="F392" s="4">
+        <v>0</v>
+      </c>
+      <c r="H392" s="19">
+        <v>1</v>
+      </c>
+      <c r="I392" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J392" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K392" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L392" s="4" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I17 I19:I32 I34:I39 I41:I46 I48:I53 I55:I60 I62:I67 I69:I74 I76:I81 I83:I102 I104:I117 I119:I124 I126:I131 I133:I138 I140:I145 I147:I152 I154:I159 I161:I166 I168:I186 I188:I201 I203:I208 I210:I215 I217:I222 I224:I229 I231:I236 I238:I243 I245:I250 I252:I255 K28:K87 L2:L245">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I17 I19:I32 I34:I39 I41:I46 I48:I53 I55:I60 I62:I67 I69:I74 I76:I81 I83:I102 I104:I117 I119:I124 I126:I131 I133:I138 I140:I145 I147:I152 I154:I159 I161:I166 I168:I186 I188:I201 I203:I208 I210:I215 I217:I222 I224:I229 I231:I236 I238:I243 K28:K87 L2:L392 I245:I249 I251:I256 I258:I263 I265:I273 I275:I280 I282:I287 I289:I297 I299:I304 I306:I308 I310:I318 I320:I325 I327:I329 I331:I339 I341:I346 I348:I351 I353:I361 I363:I368 I370:I372 I374:I382 I384:I389 I391:I392">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>